--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q40_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009450577666866307</v>
+        <v>0.008630675027576954</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009450577666866307</v>
+        <v>0.008630675027576954</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004836818522844819</v>
+        <v>0.004486989389860551</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.008789756130272828</v>
+        <v>0.007945570719294772</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008789756130272828</v>
+        <v>0.007945570719294772</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003321387377447009</v>
+        <v>0.003033032044140705</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01065163874566612</v>
+        <v>0.009718224192092379</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01065163874566612</v>
+        <v>0.009718224192092379</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00234587669989149</v>
+        <v>0.002467486231862822</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01661479386477293</v>
+        <v>0.01546944036023315</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01661479386477293</v>
+        <v>0.01546944036023315</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003178745541448746</v>
+        <v>0.003166841505072349</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02531536052424492</v>
+        <v>0.02359381383813474</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02531536052424492</v>
+        <v>0.02359381383813474</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006382357291651787</v>
+        <v>0.006201839524769291</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03443457424265542</v>
+        <v>0.03193155954312963</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03443457424265542</v>
+        <v>0.03193155954312963</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005173489709054017</v>
+        <v>0.005029330015553871</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04648518555417931</v>
+        <v>0.04312040867822741</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04648518555417931</v>
+        <v>0.04312040867822741</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004755750887780571</v>
+        <v>0.004536009767391426</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05815155688772495</v>
+        <v>0.05407692994152687</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05815155688772495</v>
+        <v>0.05407692994152687</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00645591094272234</v>
+        <v>0.006081298104336516</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.06646320203545605</v>
+        <v>0.06186608545021708</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06646320203545605</v>
+        <v>0.06186608545021708</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007758768488182962</v>
+        <v>0.007071517072918873</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.07057023291582244</v>
+        <v>0.06563307884392761</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07057023291582244</v>
+        <v>0.06563307884392761</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008767693397385135</v>
+        <v>0.007693060813428</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.07039585543329874</v>
+        <v>0.06537885431693366</v>
       </c>
       <c r="C12" t="n">
-        <v>0.07039585543329874</v>
+        <v>0.06537885431693366</v>
       </c>
       <c r="D12" t="n">
-        <v>0.009267774472491963</v>
+        <v>0.007871689329080288</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.06826433095821667</v>
+        <v>0.06336191055000015</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06826433095821667</v>
+        <v>0.06336191055000015</v>
       </c>
       <c r="D13" t="n">
-        <v>0.009162001585557644</v>
+        <v>0.007514658967423322</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0653632827100239</v>
+        <v>0.06069589198130731</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0653632827100239</v>
+        <v>0.06069589198130731</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008908455629267481</v>
+        <v>0.007162034288876289</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0610234872634659</v>
+        <v>0.05669057878119831</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0610234872634659</v>
+        <v>0.05669057878119831</v>
       </c>
       <c r="D15" t="n">
-        <v>0.008481908557815637</v>
+        <v>0.006925154593674821</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.05978052540516567</v>
+        <v>0.05557990550880271</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05978052540516567</v>
+        <v>0.05557990550880271</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00844010432997847</v>
+        <v>0.006979523647239659</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05610878409865883</v>
+        <v>0.05219972696108927</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05610878409865883</v>
+        <v>0.05219972696108927</v>
       </c>
       <c r="D17" t="n">
-        <v>0.008178216147175163</v>
+        <v>0.00692780967441227</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.05384476182532093</v>
+        <v>0.0501336150591935</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05384476182532093</v>
+        <v>0.0501336150591935</v>
       </c>
       <c r="D18" t="n">
-        <v>0.008239733590043272</v>
+        <v>0.006953484809986117</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.05514737277857868</v>
+        <v>0.05137093753949089</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05514737277857868</v>
+        <v>0.05137093753949089</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008583930192690136</v>
+        <v>0.007270025690020009</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0517642038610644</v>
+        <v>0.04825692181813501</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0517642038610644</v>
+        <v>0.04825692181813501</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0086624628772622</v>
+        <v>0.007410110706857021</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.05050076962559758</v>
+        <v>0.04723706157541661</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05050076962559758</v>
+        <v>0.04723706157541661</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00879195479082303</v>
+        <v>0.007468057237964021</v>
       </c>
     </row>
   </sheetData>
